--- a/data/config.xlsx
+++ b/data/config.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="历史审核结果" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'模块化功能'!$A$1:$F$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'执行流程'!$A$1:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'模块化功能'!$A$1:$F$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'执行流程'!$A$1:$I$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'自定义按钮'!$A$1:$D$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'历史审核结果'!$A$1:$L$2</definedName>
   </definedNames>
@@ -191,6 +191,7 @@
 核对_表结构比对：逐格核对固定表头，不匹配的报送文件跳过；
 修改_外部文件添加：把外部工作表复制进审核副本，须先于公式校验复制；
 修改_公式校验复制：复制模板公式并强制重算，可输出同名审核副本目录；
+修改_合并同机构多表：按文件名第一段识别机构，将同一机构多个工作簿的所有工作表合并为一本；
 汇总_公式校验结果提取：重算后提取错误、核实、提示等结果；
 汇总_任意行汇总 / 汇总_固定行汇总 / 汇总_汇总表合并：区域汇总。</t>
       </text>
@@ -252,12 +253,12 @@
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>只对会产出实际文件的功能生效：外部文件添加 / 公式校验复制输出同名阶段副本目录、审核副本目录，校验结果提取输出同名本期审核结果工作簿；填“否”时这些中间文件处理完即清理。检查类与表结构比对始终只记入运行日志，不受此列影响。</t>
+        <t>只对会产出实际文件的功能生效：外部文件添加 / 公式校验复制输出同名阶段副本目录、审核副本目录，校验结果提取和合并同机构多表输出实际工作簿；填“否”时这些中间文件处理完即清理。检查类与表结构比对始终只记入运行日志，不受此列影响。</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>输出文件名（可选）：仅对“是否输出结果=是”且会产出实际文件的步骤生效；填写后，该步骤的输出文件/目录名从“序号_功能名_时间戳”改为“输出文件名_时间戳”。校验结果提取、任意行/固定行/汇总表合并等最终结果建议填流程名；外部文件添加、公式校验复制的中间阶段副本默认留空。</t>
+        <t>输出文件名（可选）：仅对“是否输出结果=是”且会产出实际文件的步骤生效；填写后，该步骤的输出文件/目录名从“序号_功能名_时间戳”改为“输出文件名_时间戳”。校验结果提取、任意行/固定行/汇总表合并、合并同机构多表等最终结果建议填流程名；外部文件添加、公式校验复制的中间阶段副本默认留空。</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
@@ -625,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -940,8 +941,32 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>合并同机构多表</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>修改_合并同机构多表</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr"/>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>把源目录下同一机构（文件名主名下划线第一段相同）的所有工作簿合并为一本，所有工作表集中存放，供制作模板后单独跑汇总核查表校验</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F11"/>
+  <autoFilter ref="A1:F12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -953,7 +978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="20" customWidth="1" style="1" min="1" max="1"/>
@@ -1487,8 +1512,49 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>合并同机构多表</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>合并同机构多表</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>停止</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>合并同机构多表</t>
+        </is>
+      </c>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>递归合并同一机构的多个报送工作簿为一本，输出每机构一个 xlsx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I14"/>
+  <autoFilter ref="A1:I15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
